--- a/docs/StructureDefinition-NoImplVitalSignsObservationQSOFAScore.xlsx
+++ b/docs/StructureDefinition-NoImplVitalSignsObservationQSOFAScore.xlsx
@@ -2871,17 +2871,17 @@
   <dimension ref="A1:AP225"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="59.5" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="41.515625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="18.390625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.55078125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="58.30078125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.64453125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="18.0234375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="129.546875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="122.43359375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2890,28 +2890,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="34.80859375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="85.70703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.55078125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="13.44140625" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="36.046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="8.51953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="8.859375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="32.7734375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="47.7421875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="23.9609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="214.97265625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="93.1640625" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="29.45703125" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="33.8203125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
